--- a/e2e-screenshots/accessory-return-reconcile/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/accessory-return-reconcile/downloaded-sales-report.xlsx
@@ -10,16 +10,17 @@
     <sheet sheetId="4" name="EBAY" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="ONBUY" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="TEMU" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Returns Summary" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Returns Detail" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Unit Histories" state="visible" r:id="rId12"/>
+    <sheet sheetId="7" name="Accessories" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Returns Summary" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Returns Detail" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Unit Histories" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="103">
   <si>
     <t>Sales Report — Audit Summary</t>
   </si>
@@ -162,6 +163,9 @@
     <t>Comments</t>
   </si>
   <si>
+    <t>Model</t>
+  </si>
+  <si>
     <t>Return Date</t>
   </si>
   <si>
@@ -177,6 +181,12 @@
     <t>Postage Loss</t>
   </si>
   <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Colour</t>
+  </si>
+  <si>
     <t>ACC-RET-9001</t>
   </si>
   <si>
@@ -222,6 +232,12 @@
     <t>Commission VAT</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>USB-C 20W Charger</t>
+  </si>
+  <si>
     <t>Period</t>
   </si>
   <si>
@@ -273,7 +289,7 @@
     <t>Carriage costed from</t>
   </si>
   <si>
-    <t>2026-07-28</t>
+    <t>2026-07-29</t>
   </si>
   <si>
     <t>Uncosted (pre-tracking) returns</t>
@@ -282,15 +298,6 @@
     <t>Unit IMEI</t>
   </si>
   <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Storage</t>
-  </si>
-  <si>
-    <t>Colour</t>
-  </si>
-  <si>
     <t>Original Sale Date</t>
   </si>
   <si>
@@ -304,9 +311,6 @@
   </si>
   <si>
     <t>Leg Cost £</t>
-  </si>
-  <si>
-    <t>USB-C 20W Charger</t>
   </si>
   <si>
     <t>Accessory</t>
@@ -331,8 +335,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -389,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -402,6 +407,7 @@
     <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1030,12 +1036,51 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1118,24 +1163,33 @@
         <v>51</v>
       </c>
       <c r="AB1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AD1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>46225.5</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F2" s="8">
         <v>3</v>
@@ -1180,34 +1234,43 @@
         <f>I2-J2-K2-L2-M2-N2-O2-P2-Q2</f>
       </c>
       <c r="T2" s="10">
-        <f>(S2-AA2)/G2*100</f>
+        <f>(S2-AB2)/G2*100</f>
       </c>
       <c r="U2" s="10">
         <f>J2-R2</f>
       </c>
       <c r="V2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" s="7">
-        <v>46231.5</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>55</v>
+        <v>58</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="X2" s="7">
+        <v>46232.5</v>
       </c>
       <c r="Y2" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z2" s="8">
+        <v>58</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA2" s="8">
         <v>2</v>
       </c>
-      <c r="AA2" s="10">
+      <c r="AB2" s="10">
         <v>6</v>
       </c>
-      <c r="AB2" s="10">
-        <f>S2-AA2</f>
-      </c>
-    </row>
-    <row r="3" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC2" s="10">
+        <f>S2-AB2</f>
+      </c>
+      <c r="AD2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -1258,7 +1321,7 @@
         <f>SUM(S2:S2)</f>
       </c>
       <c r="T3" s="11">
-        <f>IFERROR((S3-AA3)/G3*100,0)</f>
+        <f>IFERROR((S3-AB3)/G3*100,0)</f>
       </c>
       <c r="U3" s="11">
         <f>SUM(U2:U2)</f>
@@ -1268,12 +1331,15 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
-      <c r="AA3" s="11">
-        <f>SUM(AA2:AA2)</f>
-      </c>
+      <c r="AA3" s="6"/>
       <c r="AB3" s="11">
         <f>SUM(AB2:AB2)</f>
       </c>
+      <c r="AC3" s="11">
+        <f>SUM(AC2:AC2)</f>
+      </c>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1283,10 +1349,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1321,7 +1387,7 @@
         <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M1" t="s">
         <v>39</v>
@@ -1360,7 +1426,16 @@
         <v>51</v>
       </c>
       <c r="Y1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z1" t="s">
         <v>10</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1371,10 +1446,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1391,7 +1466,7 @@
         <v>29</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G1" t="s">
         <v>31</v>
@@ -1409,16 +1484,16 @@
         <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="O1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P1" t="s">
         <v>39</v>
@@ -1427,10 +1502,10 @@
         <v>40</v>
       </c>
       <c r="R1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="S1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="T1" t="s">
         <v>41</v>
@@ -1466,7 +1541,16 @@
         <v>51</v>
       </c>
       <c r="AE1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF1" t="s">
         <v>10</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1477,10 +1561,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1512,7 +1596,7 @@
         <v>35</v>
       </c>
       <c r="K1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L1" t="s">
         <v>39</v>
@@ -1554,7 +1638,16 @@
         <v>51</v>
       </c>
       <c r="Y1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z1" t="s">
         <v>10</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1565,10 +1658,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1603,7 +1696,7 @@
         <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M1" t="s">
         <v>39</v>
@@ -1645,7 +1738,16 @@
         <v>51</v>
       </c>
       <c r="Z1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA1" t="s">
         <v>10</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1655,6 +1757,137 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>46225.5</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="8">
+        <v>3</v>
+      </c>
+      <c r="H2" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="I2" s="10">
+        <v>8.99</v>
+      </c>
+      <c r="J2" s="10">
+        <v>-0.2</v>
+      </c>
+      <c r="K2" s="12">
+        <v>-5.58</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <f>SUM(G2:G2)</f>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(H2:H2)</f>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(I2:I2)</f>
+      </c>
+      <c r="J3" s="11">
+        <f>SUM(J2:J2)</f>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1665,15 +1898,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1705,7 +1938,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B6" s="3">
         <v>6</v>
@@ -1713,7 +1946,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3">
         <v>6</v>
@@ -1721,10 +1954,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1732,12 +1965,12 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1745,31 +1978,31 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
@@ -1777,129 +2010,18 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B19">
         <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L1" t="s">
-        <v>93</v>
-      </c>
-      <c r="M1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N1" t="s">
-        <v>94</v>
-      </c>
-      <c r="O1" t="s">
-        <v>50</v>
-      </c>
-      <c r="P1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>46231.5</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" s="7">
-        <v>46225.5</v>
-      </c>
-      <c r="H2" s="10">
-        <v>8.99</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" s="10">
-        <v>3</v>
-      </c>
-      <c r="O2" s="8">
-        <v>2</v>
-      </c>
-      <c r="P2" s="10">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1910,35 +2032,107 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>46232.5</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="7">
+        <v>46225.5</v>
+      </c>
+      <c r="H2" s="10">
+        <v>8.99</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>101</v>
+      <c r="K2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="10">
+        <v>3</v>
+      </c>
+      <c r="O2" s="8">
+        <v>2</v>
+      </c>
+      <c r="P2" s="10">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/accessory-return-reconcile/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/accessory-return-reconcile/downloaded-sales-report.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="105">
   <si>
     <t>Sales Report — Audit Summary</t>
   </si>
@@ -259,7 +259,7 @@
     <t>Returns · Loss £</t>
   </si>
   <si>
-    <t>1 · £6.00</t>
+    <t>1 · £0.00</t>
   </si>
   <si>
     <t>Carriage cost policy</t>
@@ -289,10 +289,16 @@
     <t>Carriage costed from</t>
   </si>
   <si>
-    <t>2026-07-29</t>
+    <t>no costed returns in this period</t>
   </si>
   <si>
     <t>Uncosted (pre-tracking) returns</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>1 return predate carriage tracking and contribute £0 — lifetime loss understates these.</t>
   </si>
   <si>
     <t>Unit IMEI</t>
@@ -339,7 +345,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -353,6 +359,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFB45309"/>
     </font>
     <font>
       <i/>
@@ -394,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -409,6 +419,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -841,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
         <v>0</v>
@@ -986,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
@@ -1043,30 +1054,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s">
         <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>102</v>
+      <c r="A2" s="14" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1219,7 +1230,7 @@
         <f>M2*20%</f>
       </c>
       <c r="O2" s="10">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P2" s="10">
         <f>O2*20%</f>
@@ -1257,9 +1268,7 @@
       <c r="AA2" s="8">
         <v>2</v>
       </c>
-      <c r="AB2" s="10">
-        <v>6</v>
-      </c>
+      <c r="AB2" s="8"/>
       <c r="AC2" s="10">
         <f>S2-AB2</f>
       </c>
@@ -1834,10 +1843,10 @@
         <v>8.99</v>
       </c>
       <c r="J2" s="10">
-        <v>-0.2</v>
+        <v>2.8</v>
       </c>
       <c r="K2" s="12">
-        <v>-5.58</v>
+        <v>80.13</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>58</v>
@@ -1889,7 +1898,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1941,7 +1950,7 @@
         <v>75</v>
       </c>
       <c r="B6" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1949,7 +1958,7 @@
         <v>76</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2020,8 +2029,16 @@
       <c r="A19" t="s">
         <v>90</v>
       </c>
-      <c r="B19">
-        <v>0</v>
+      <c r="B19" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2040,7 +2057,7 @@
         <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
         <v>47</v>
@@ -2055,28 +2072,28 @@
         <v>29</v>
       </c>
       <c r="G1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I1" t="s">
         <v>3</v>
       </c>
       <c r="J1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K1" t="s">
         <v>49</v>
       </c>
       <c r="L1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M1" t="s">
         <v>46</v>
       </c>
       <c r="N1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O1" t="s">
         <v>51</v>
@@ -2114,7 +2131,7 @@
         <v>12</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>58</v>
@@ -2125,15 +2142,11 @@
       <c r="M2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="10">
-        <v>3</v>
-      </c>
+      <c r="N2" s="10"/>
       <c r="O2" s="8">
         <v>2</v>
       </c>
-      <c r="P2" s="10">
-        <v>6</v>
-      </c>
+      <c r="P2" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/e2e-screenshots/accessory-return-reconcile/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/accessory-return-reconcile/downloaded-sales-report.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="103">
   <si>
     <t>Sales Report — Audit Summary</t>
   </si>
@@ -259,7 +259,7 @@
     <t>Returns · Loss £</t>
   </si>
   <si>
-    <t>1 · £0.00</t>
+    <t>1 · £6.00</t>
   </si>
   <si>
     <t>Carriage cost policy</t>
@@ -289,16 +289,10 @@
     <t>Carriage costed from</t>
   </si>
   <si>
-    <t>no costed returns in this period</t>
+    <t>2026-07-29</t>
   </si>
   <si>
     <t>Uncosted (pre-tracking) returns</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>1 return predate carriage tracking and contribute £0 — lifetime loss understates these.</t>
   </si>
   <si>
     <t>Unit IMEI</t>
@@ -345,7 +339,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -359,10 +353,6 @@
     </font>
     <font>
       <b/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFB45309"/>
     </font>
     <font>
       <i/>
@@ -404,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -419,7 +409,6 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -852,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H5" s="3">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="I5" s="3">
         <v>0</v>
@@ -997,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
@@ -1054,30 +1043,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
         <v>47</v>
       </c>
       <c r="C1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" t="s">
         <v>100</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>101</v>
-      </c>
-      <c r="E1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F1" t="s">
-        <v>103</v>
       </c>
       <c r="G1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>104</v>
+      <c r="A2" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1230,7 +1219,7 @@
         <f>M2*20%</f>
       </c>
       <c r="O2" s="10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P2" s="10">
         <f>O2*20%</f>
@@ -1268,7 +1257,9 @@
       <c r="AA2" s="8">
         <v>2</v>
       </c>
-      <c r="AB2" s="8"/>
+      <c r="AB2" s="10">
+        <v>6</v>
+      </c>
       <c r="AC2" s="10">
         <f>S2-AB2</f>
       </c>
@@ -1843,10 +1834,10 @@
         <v>8.99</v>
       </c>
       <c r="J2" s="10">
-        <v>2.8</v>
+        <v>-0.2</v>
       </c>
       <c r="K2" s="12">
-        <v>80.13</v>
+        <v>-5.58</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>58</v>
@@ -1898,7 +1889,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1950,7 +1941,7 @@
         <v>75</v>
       </c>
       <c r="B6" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1958,7 +1949,7 @@
         <v>76</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2029,16 +2020,8 @@
       <c r="A19" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" t="s">
-        <v>92</v>
+      <c r="B19">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2057,7 +2040,7 @@
         <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
         <v>47</v>
@@ -2072,28 +2055,28 @@
         <v>29</v>
       </c>
       <c r="G1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I1" t="s">
         <v>3</v>
       </c>
       <c r="J1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K1" t="s">
         <v>49</v>
       </c>
       <c r="L1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M1" t="s">
         <v>46</v>
       </c>
       <c r="N1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O1" t="s">
         <v>51</v>
@@ -2131,7 +2114,7 @@
         <v>12</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>58</v>
@@ -2142,11 +2125,15 @@
       <c r="M2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="10"/>
+      <c r="N2" s="10">
+        <v>3</v>
+      </c>
       <c r="O2" s="8">
         <v>2</v>
       </c>
-      <c r="P2" s="10"/>
+      <c r="P2" s="10">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
